--- a/docs/Files/ODYM_Tutorial6_LifetimeLL_V1.0.xlsx
+++ b/docs/Files/ODYM_Tutorial6_LifetimeLL_V1.0.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DFC758-47D2-4AAD-A4C0-4567C5EC048D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C4612EA-5793-42F9-BF80-9711F3A4BA2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="101">
   <si>
     <t>Format_Version</t>
   </si>
@@ -321,24 +321,6 @@
     <t>Western Europe values taken as proxy for global region</t>
   </si>
   <si>
-    <t>construction</t>
-  </si>
-  <si>
-    <t>products and other</t>
-  </si>
-  <si>
-    <t>3;75;22.5;none</t>
-  </si>
-  <si>
-    <t>3;15;4.5;none</t>
-  </si>
-  <si>
-    <t>3_LT_SteelCycle_PAULIUK_2013, from sector "buildings - construction - infrastructure", Western Europe values taken as proxy for global region</t>
-  </si>
-  <si>
-    <t>3_LT_SteelCycle_PAULIUK_2013, from sector "appliances - packaging - other", Western Europe values taken as proxy for global region</t>
-  </si>
-  <si>
     <t>ODYM_Classifications_LL</t>
   </si>
   <si>
@@ -348,13 +330,10 @@
     <t>other EV LIB products</t>
   </si>
   <si>
-    <t>assuming 15yrs for now</t>
-  </si>
-  <si>
-    <t>3;1;6.0;none</t>
-  </si>
-  <si>
-    <t>3;1;9.0;none</t>
+    <t>3;12;5.0;none</t>
+  </si>
+  <si>
+    <t>assuming 12yrs for now</t>
   </si>
 </sst>
 </file>
@@ -985,7 +964,7 @@
         <v>39</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>18</v>
@@ -1146,7 +1125,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.36328125" customWidth="1"/>
@@ -1181,10 +1160,10 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="17" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -1193,18 +1172,18 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="F2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -1213,50 +1192,10 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="F3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F4" t="s">
         <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>99</v>
-      </c>
-      <c r="F5" t="s">
-        <v>101</v>
       </c>
     </row>
   </sheetData>
